--- a/Data/FM/FM_Quizzes.xlsx
+++ b/Data/FM/FM_Quizzes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\Semester 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\FM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC2B8FD-0DE2-4611-A0CC-8D86A8270B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DD5962-33A4-46BD-BFDA-F6302B8825B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="757" firstSheet="1" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="757" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="26" r:id="rId1"/>
@@ -27,9 +27,9 @@
     <sheet name="Week 12" sheetId="37" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'Week 1'!$A$1:$H$21</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'Week 1'!$A$1:$G$21</definedName>
     <definedName name="ExternalData_10" localSheetId="9" hidden="1">'Week 10'!$A$1:$F$21</definedName>
-    <definedName name="ExternalData_11" localSheetId="10" hidden="1">'Week 11'!$A$1:$H$21</definedName>
+    <definedName name="ExternalData_11" localSheetId="10" hidden="1">'Week 11'!$A$1:$G$21</definedName>
     <definedName name="ExternalData_12" localSheetId="11" hidden="1">'Week 12'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_2" localSheetId="1" hidden="1">'Week 2'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_3" localSheetId="2" hidden="1">'Week 3'!$A$1:$F$21</definedName>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="1040">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -167,9 +167,6 @@
     <t xml:space="preserve">Question 5 </t>
   </si>
   <si>
-    <t xml:space="preserve">This question has been regraded. </t>
-  </si>
-  <si>
     <t>State the various short term investment in the company</t>
   </si>
   <si>
@@ -3173,9 +3170,6 @@
     <t>Sales – Cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Original Score:  Regraded Score:  </t>
-  </si>
-  <si>
     <t>QuestionID</t>
   </si>
   <si>
@@ -3194,12 +3188,6 @@
     <t>Option_D</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -3222,6 +3210,21 @@
   </si>
   <si>
     <t>1010</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -3322,7 +3325,7 @@
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="12" xr16:uid="{EBE29F36-CBB6-4DEB-97CC-7A78B59C8F39}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9">
-    <queryTableFields count="8">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
@@ -3330,22 +3333,25 @@
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
       <queryTableField id="7" name="6" tableColumnId="7"/>
-      <queryTableField id="8" name="7" tableColumnId="8"/>
     </queryTableFields>
+    <queryTableDeletedFields count="1">
+      <deletedField name="7"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_10" connectionId="11" xr16:uid="{4EFCE436-0A9F-44F0-9A41-C23D08D5ECD2}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3354,7 +3360,7 @@
 <file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_11" connectionId="2" xr16:uid="{A427DB0F-ADA2-4FFB-8F66-90BAEF2AE8F5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9">
-    <queryTableFields count="8">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
@@ -3362,22 +3368,25 @@
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
       <queryTableField id="7" name="6" tableColumnId="7"/>
-      <queryTableField id="8" name="7" tableColumnId="8"/>
     </queryTableFields>
+    <queryTableDeletedFields count="1">
+      <deletedField name="7"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_12" connectionId="3" xr16:uid="{5211BCF9-ACBA-4D3A-8DEA-DFC7436AA418}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3385,14 +3394,15 @@
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="1" xr16:uid="{1232A902-17E7-4E26-B404-D1593E7B33CB}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3400,14 +3410,15 @@
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="4" xr16:uid="{DFCBAFAB-F6C4-4564-930E-3EC9FE887F2A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3415,14 +3426,15 @@
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_4" connectionId="5" xr16:uid="{635130D3-AF36-4D5E-93E7-108637FA00DA}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3430,14 +3442,15 @@
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_5" connectionId="6" xr16:uid="{7E07CBE5-4A27-4A95-BD7B-9020CFF9DC00}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3445,14 +3458,15 @@
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_6" connectionId="7" xr16:uid="{78EB8A38-D408-43BB-AA99-3B464D5E215E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3460,14 +3474,15 @@
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_7" connectionId="8" xr16:uid="{138981D2-1CEC-45B5-87D0-673FB275A451}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3475,14 +3490,15 @@
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_8" connectionId="9" xr16:uid="{1F126A00-446C-4AC6-BF77-E41DA83298DA}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3490,198 +3506,207 @@
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_9" connectionId="10" xr16:uid="{71E99A29-C927-4368-8C19-8C468571F035}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{63EC1C8D-A8CD-43FA-A1B1-28B0E604F8EB}" name="Invoked_FunctionQuery1" displayName="Invoked_FunctionQuery1" ref="A1:H21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H21" xr:uid="{63EC1C8D-A8CD-43FA-A1B1-28B0E604F8EB}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{0B0F324B-E1E8-4274-9B6B-5190B616D6EE}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{63EC1C8D-A8CD-43FA-A1B1-28B0E604F8EB}" name="Invoked_FunctionQuery1" displayName="Invoked_FunctionQuery1" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{63EC1C8D-A8CD-43FA-A1B1-28B0E604F8EB}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{0B0F324B-E1E8-4274-9B6B-5190B616D6EE}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{F740AA24-08B7-45E9-B075-4A2744B3E586}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{A49013DD-A5EE-4E4D-B123-059F6F1D7EDB}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{248B5DEC-50F5-4147-ABC7-491DA6D55500}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{B19E08D2-8414-4FAF-8C5D-236FC9C6CFD2}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{841853DA-DD3F-4284-AEB9-39233C77EB00}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{24B1D09E-86EE-4815-91D8-524887C3B927}" uniqueName="7" name="6" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{68872975-0D1F-45CD-9137-EA1BF54C1FE6}" uniqueName="8" name="7" queryTableFieldId="8"/>
+    <tableColumn id="7" xr3:uid="{24B1D09E-86EE-4815-91D8-524887C3B927}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{017D5C77-CB0B-402E-834D-A15D50F5641F}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{017D5C77-CB0B-402E-834D-A15D50F5641F}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{455AAFE5-40EA-45C1-BB67-3AA5BB08AAAC}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{017D5C77-CB0B-402E-834D-A15D50F5641F}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{017D5C77-CB0B-402E-834D-A15D50F5641F}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{455AAFE5-40EA-45C1-BB67-3AA5BB08AAAC}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{69D6F014-6AD2-45E3-9D63-2816FE591192}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{55D809B5-6578-4F90-8311-041B24B1C6D8}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{AEBD9F8B-A433-4E8B-BC2E-4C9F0CB1CBD2}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{E47B25D7-7974-4C1C-848A-5F3427EA0016}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{6981B6A8-6BE4-43E9-965F-E77A563B9A48}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{980BF7BD-C19F-4791-B636-E4A22FB88161}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{E1E1CE77-F73A-4C77-B7C6-D62035F7A306}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:H21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H21" xr:uid="{E1E1CE77-F73A-4C77-B7C6-D62035F7A306}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A3BE2E0E-9AA3-4D1B-A484-F9FD1084EDBF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{E1E1CE77-F73A-4C77-B7C6-D62035F7A306}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{E1E1CE77-F73A-4C77-B7C6-D62035F7A306}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{A3BE2E0E-9AA3-4D1B-A484-F9FD1084EDBF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{E12C8D8B-9C25-45FB-9FAD-05645D0D9E44}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{155E75DD-3437-4080-8BFF-3A7960EBACC9}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{D8AA8A38-D9B2-4B54-A517-75118643B1EA}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{B2553020-C220-4467-8C50-A52FE44FA307}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{972C0C4B-9931-4AEA-8348-FA59F0785BB3}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{91287AD6-82A5-47C7-8864-39951034F2DA}" uniqueName="7" name="6" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{E02BAFDC-C9FE-4D96-8988-8FD69032E312}" uniqueName="8" name="7" queryTableFieldId="8"/>
+    <tableColumn id="7" xr3:uid="{91287AD6-82A5-47C7-8864-39951034F2DA}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{67AB4AF6-7B9D-4850-BDC4-FBB9B831EFBF}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{67AB4AF6-7B9D-4850-BDC4-FBB9B831EFBF}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00EC8F79-0F3F-4A99-8F25-0D3FF9746F88}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{67AB4AF6-7B9D-4850-BDC4-FBB9B831EFBF}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{67AB4AF6-7B9D-4850-BDC4-FBB9B831EFBF}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00EC8F79-0F3F-4A99-8F25-0D3FF9746F88}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{3E0A8AE2-A129-4867-A441-234C7C525CF2}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{8662F21C-DEC6-4ED2-8FFE-3C98A97EFC59}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{9CDA9D71-2DD8-4C4F-A45F-BFBBD2361D0C}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{0E00B5B1-14BF-4F9C-8160-A71A65263321}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{93CDF502-C562-4D85-B677-FEA16568F093}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{F84D7229-EF53-40E1-8464-0E415C839F1A}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{CE4733E6-32BE-45FE-AA55-0A6BED8407E2}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{CE4733E6-32BE-45FE-AA55-0A6BED8407E2}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{970B163D-4323-4439-ACCC-57144CBFC96C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{CE4733E6-32BE-45FE-AA55-0A6BED8407E2}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{CE4733E6-32BE-45FE-AA55-0A6BED8407E2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{970B163D-4323-4439-ACCC-57144CBFC96C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{3B6AE74A-F231-4EBC-9C83-292BDE188133}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{DB3BBDA9-7631-451D-B577-BDE147CFED88}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7D7A4AAE-0514-45B7-884C-69037B40B09F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{5A2C6EE3-2F13-46CF-BAD4-C8AA44687E78}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{48CBB9C2-F899-427D-A985-7C3138826813}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{1B41D469-D68C-4AA6-BA7D-314F2ADDCC98}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AFBB01ED-FD1B-447E-8286-C2818ABDE744}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{AFBB01ED-FD1B-447E-8286-C2818ABDE744}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E19626C5-FCE8-44CF-A56F-23C57B0BC645}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AFBB01ED-FD1B-447E-8286-C2818ABDE744}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{AFBB01ED-FD1B-447E-8286-C2818ABDE744}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E19626C5-FCE8-44CF-A56F-23C57B0BC645}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{D96BCFFE-2E7C-450A-A9F7-94A50DCF15CB}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F5701FBF-B3DF-4158-AEB1-A94BD33E998F}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{1ACA846A-1510-4EDF-8887-8A4E7FE37C12}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{3583F810-4626-401F-9415-6B681FE62E86}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{655F8B80-BB72-4CC7-BB6D-220796ABF6CB}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{82999FAB-4DD2-477D-B3BA-4DA8FEA7ABE8}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{FEB41DDA-B23B-492D-926A-4D66FE12C87B}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{FEB41DDA-B23B-492D-926A-4D66FE12C87B}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F9816592-9F0B-4B65-BCFF-117EA765AC46}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{FEB41DDA-B23B-492D-926A-4D66FE12C87B}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{FEB41DDA-B23B-492D-926A-4D66FE12C87B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{F9816592-9F0B-4B65-BCFF-117EA765AC46}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{324013E0-A8F5-4485-AF7B-8B702970A320}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{BF1653F1-0A98-47E6-85C3-F558B4E0B464}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{0346CF58-1703-49DE-8ED6-980B795B8087}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{348FA271-CCE6-4EE5-BA46-3B493F2C46B2}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{D33C24DC-032F-49BB-A537-CAA59C185FE6}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{F7790177-5BEE-4B9A-888D-F5174BA199BA}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{0BEF02E7-AA42-46C0-82A2-FF4ABD983B81}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{0BEF02E7-AA42-46C0-82A2-FF4ABD983B81}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2BA36A9E-F952-41A9-9285-D4EB5EDFD6FE}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{0BEF02E7-AA42-46C0-82A2-FF4ABD983B81}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{0BEF02E7-AA42-46C0-82A2-FF4ABD983B81}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{2BA36A9E-F952-41A9-9285-D4EB5EDFD6FE}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{08C29924-8CE5-45CB-8D89-E21396FBD34F}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{4F59FA37-D0CA-4C6A-9049-8BAB5A127AA6}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{B38EFD44-4925-4804-B22B-72DC6D40ED1E}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{7377ED27-78F8-4A2E-9F75-914A8D6340EC}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{833E474A-3954-415F-B201-4C977F3367CC}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{165ECDA4-F57F-4F59-B535-58DFCFB534B1}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{0BDEB42C-11DB-466E-9C74-432BD0989372}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{0BDEB42C-11DB-466E-9C74-432BD0989372}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{5FEA64B8-065A-4B6F-9CBA-BF6043B59267}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{0BDEB42C-11DB-466E-9C74-432BD0989372}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{0BDEB42C-11DB-466E-9C74-432BD0989372}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{5FEA64B8-065A-4B6F-9CBA-BF6043B59267}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{E0739EFC-8D32-4632-A844-8680B1137F0E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E82EF2A1-E038-495D-B269-44CB6F0E100D}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7A8E0AC3-28C6-46E2-AEFA-5333A076C763}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{77AAFDD8-605E-4766-8825-3D317DCCC724}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{783F0FB3-D673-4CDD-8D1E-FE437E28A412}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{75599BEC-47AF-4B6D-8CE5-250A54B7D628}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{52C2454F-E770-43E2-9BB5-590374E7D771}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{52C2454F-E770-43E2-9BB5-590374E7D771}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{54A5AC94-05DB-472C-B51F-A1F09CAE24E2}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{52C2454F-E770-43E2-9BB5-590374E7D771}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{52C2454F-E770-43E2-9BB5-590374E7D771}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{54A5AC94-05DB-472C-B51F-A1F09CAE24E2}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{757ADCB9-2554-4E5E-A83E-C2DB4D02C1FD}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{1EE8A824-3E1F-47BD-9F16-29D0E60BCCE0}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{4DD5E5A0-1640-48A3-B08B-75FCCD70538F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{ABAA68C2-8750-42C0-B8B7-D07AF4138FF4}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{76D0C744-7004-4BD9-BF39-7EC2C0418104}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{E4D26F7B-3A2F-47C6-B17B-D830A9E53588}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{FF4F6A93-5234-4040-B178-F05987A6590E}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{FF4F6A93-5234-4040-B178-F05987A6590E}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{101C3727-056A-4416-BD57-3EAE5F6454E6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{FF4F6A93-5234-4040-B178-F05987A6590E}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{FF4F6A93-5234-4040-B178-F05987A6590E}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{101C3727-056A-4416-BD57-3EAE5F6454E6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{0F2F95F3-90A7-40FE-8826-318209EB5E6D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E123AC86-ED60-48F7-A0B5-47FD96E81FD2}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7B966358-95EC-4170-BC56-B8D418D75480}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{6CA8820D-320F-4CE4-8007-E4DAA3CF4B02}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{CA1563C1-CA4F-49B7-ABAE-318153125909}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{8AE70138-C87B-4AE6-9194-A403A0D3755F}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{8B983792-F360-4E8B-8EC5-81F4D09C656B}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{8B983792-F360-4E8B-8EC5-81F4D09C656B}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{75936BAC-13D6-4E20-AB43-BB62C3BEB91E}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{8B983792-F360-4E8B-8EC5-81F4D09C656B}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{8B983792-F360-4E8B-8EC5-81F4D09C656B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{75936BAC-13D6-4E20-AB43-BB62C3BEB91E}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{6601D933-532D-4A74-AC60-9BF62DEA6372}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{7532B0F2-8FFC-488B-ACA2-53DE1C59C155}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{DDCE17E7-A1DE-4ADA-8073-F1CADB22105F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{DCE0CB08-A702-46CC-A842-E9DC131753BA}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{092FE0A4-9DD2-478D-97ED-86CC9E7E02C4}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{ABBEE73C-6DD8-4C85-BFAF-586F633D0532}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4005,7 +4030,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACCC6E92-4D3D-4A9F-8ADC-974D206B4449}">
   <sheetPr codeName="Sheet25"/>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4015,36 +4040,32 @@
     <col min="5" max="5" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
       <c r="G1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4060,8 +4081,11 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -4080,8 +4104,11 @@
       <c r="F3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4100,8 +4127,11 @@
       <c r="F4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -4120,331 +4150,376 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1022</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>41</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>42</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>47</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>53</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>54</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>56</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>57</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>58</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>59</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>60</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>62</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>63</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>64</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>65</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>66</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>68</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>69</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>70</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>71</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>72</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>74</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>75</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
         <v>76</v>
       </c>
-      <c r="D15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>77</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>79</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>80</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>81</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>82</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>83</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>85</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>86</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>87</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>88</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>89</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>91</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>92</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>93</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>94</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>95</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>97</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
         <v>98</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
         <v>76</v>
       </c>
-      <c r="D19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>99</v>
       </c>
-      <c r="F19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>100</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>101</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>102</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>103</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>104</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>106</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>107</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" t="s">
         <v>108</v>
       </c>
-      <c r="D21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>109</v>
       </c>
-      <c r="F21" t="s">
-        <v>110</v>
+      <c r="G21" t="s">
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -4458,7 +4533,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA1B4D9-5778-4286-A60D-19E29D280251}">
   <sheetPr codeName="Sheet16"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4469,424 +4544,487 @@
     <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C2" t="s">
         <v>792</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>793</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>794</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>795</v>
       </c>
-      <c r="F2" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C3" t="s">
         <v>797</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>798</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>799</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>800</v>
       </c>
-      <c r="F3" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C4" t="s">
         <v>802</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>803</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>804</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>805</v>
       </c>
-      <c r="F4" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>806</v>
+      </c>
+      <c r="C5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D5" t="s">
+        <v>685</v>
+      </c>
+      <c r="E5" t="s">
+        <v>391</v>
+      </c>
+      <c r="F5" t="s">
         <v>807</v>
       </c>
-      <c r="C5" t="s">
-        <v>457</v>
-      </c>
-      <c r="D5" t="s">
-        <v>686</v>
-      </c>
-      <c r="E5" t="s">
-        <v>392</v>
-      </c>
-      <c r="F5" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C6" t="s">
         <v>809</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>810</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>811</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>812</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>814</v>
       </c>
-      <c r="C7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" t="s">
-        <v>408</v>
-      </c>
-      <c r="F7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>810</v>
+      </c>
+      <c r="D8" t="s">
+        <v>606</v>
+      </c>
+      <c r="E8" t="s">
         <v>815</v>
       </c>
-      <c r="C8" t="s">
-        <v>811</v>
-      </c>
-      <c r="D8" t="s">
-        <v>607</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>816</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>473</v>
+      </c>
+      <c r="D9" t="s">
         <v>818</v>
       </c>
-      <c r="C9" t="s">
-        <v>474</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>819</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>820</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>822</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>823</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>529</v>
+      </c>
+      <c r="F10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>824</v>
       </c>
-      <c r="E10" t="s">
-        <v>530</v>
-      </c>
-      <c r="F10" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>825</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>826</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>827</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>598</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>828</v>
       </c>
-      <c r="F11" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>829</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E12" t="s">
+        <v>758</v>
+      </c>
+      <c r="F12" t="s">
         <v>830</v>
       </c>
-      <c r="D12" t="s">
-        <v>440</v>
-      </c>
-      <c r="E12" t="s">
-        <v>759</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>818</v>
+      </c>
+      <c r="D13" t="s">
+        <v>819</v>
+      </c>
+      <c r="E13" t="s">
+        <v>192</v>
+      </c>
+      <c r="F13" t="s">
+        <v>820</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>832</v>
       </c>
-      <c r="C13" t="s">
-        <v>819</v>
-      </c>
-      <c r="D13" t="s">
-        <v>820</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C14" t="s">
         <v>193</v>
       </c>
-      <c r="F13" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>833</v>
       </c>
-      <c r="C14" t="s">
-        <v>194</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>834</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>612</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>835</v>
       </c>
-      <c r="F14" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>816</v>
+      </c>
+      <c r="D15" t="s">
         <v>836</v>
       </c>
-      <c r="C15" t="s">
-        <v>817</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>837</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>838</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>840</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>841</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>842</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>843</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>681</v>
+      </c>
+      <c r="D17" t="s">
         <v>845</v>
       </c>
-      <c r="C17" t="s">
-        <v>682</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>846</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>847</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>849</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>850</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>851</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>852</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>854</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>391</v>
+      </c>
+      <c r="E19" t="s">
+        <v>420</v>
+      </c>
+      <c r="F19" t="s">
         <v>855</v>
       </c>
-      <c r="D19" t="s">
-        <v>392</v>
-      </c>
-      <c r="E19" t="s">
-        <v>421</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>333</v>
+      </c>
+      <c r="D20" t="s">
         <v>857</v>
       </c>
-      <c r="C20" t="s">
-        <v>334</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>858</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>407</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>859</v>
       </c>
-      <c r="F20" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>860</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>861</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>862</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>863</v>
       </c>
-      <c r="F21" t="s">
-        <v>864</v>
+      <c r="G21" t="s">
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -4900,7 +5038,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD23ADF-0811-4146-B819-093867F19179}">
   <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4910,439 +5048,489 @@
     <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
       <c r="G1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C2" t="s">
         <v>865</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E2" t="s">
         <v>866</v>
       </c>
-      <c r="D2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E2" t="s">
-        <v>867</v>
-      </c>
       <c r="F2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>867</v>
+      </c>
+      <c r="C3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D3" t="s">
         <v>868</v>
       </c>
-      <c r="C3" t="s">
-        <v>607</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>869</v>
       </c>
-      <c r="E3" t="s">
-        <v>870</v>
-      </c>
       <c r="F3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>870</v>
+      </c>
+      <c r="C4" t="s">
+        <v>758</v>
+      </c>
+      <c r="D4" t="s">
         <v>871</v>
       </c>
-      <c r="C4" t="s">
-        <v>759</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>598</v>
+      </c>
+      <c r="F4" t="s">
         <v>872</v>
       </c>
-      <c r="E4" t="s">
-        <v>599</v>
-      </c>
-      <c r="F4" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>873</v>
+      </c>
+      <c r="C5" t="s">
         <v>874</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>875</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>876</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>877</v>
       </c>
-      <c r="F5" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>878</v>
+      </c>
+      <c r="C6" t="s">
         <v>879</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>880</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>881</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>882</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" t="s">
         <v>884</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" t="s">
+        <v>623</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>885</v>
+      </c>
+      <c r="C8" t="s">
+        <v>886</v>
+      </c>
+      <c r="D8" t="s">
+        <v>887</v>
+      </c>
+      <c r="E8" t="s">
+        <v>888</v>
+      </c>
+      <c r="F8" t="s">
+        <v>889</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>890</v>
+      </c>
+      <c r="C9" t="s">
         <v>193</v>
       </c>
-      <c r="D7" t="s">
-        <v>885</v>
-      </c>
-      <c r="E7" t="s">
-        <v>247</v>
-      </c>
-      <c r="F7" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>886</v>
-      </c>
-      <c r="C8" t="s">
-        <v>887</v>
-      </c>
-      <c r="D8" t="s">
-        <v>888</v>
-      </c>
-      <c r="E8" t="s">
-        <v>889</v>
-      </c>
-      <c r="F8" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>891</v>
       </c>
-      <c r="C9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>892</v>
       </c>
-      <c r="E9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>893</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>894</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>876</v>
+      </c>
+      <c r="F10" t="s">
         <v>895</v>
       </c>
-      <c r="E10" t="s">
-        <v>877</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1022</v>
-      </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>897</v>
       </c>
       <c r="D11" t="s">
+        <v>898</v>
+      </c>
+      <c r="E11" t="s">
+        <v>899</v>
+      </c>
+      <c r="F11" t="s">
+        <v>900</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>901</v>
+      </c>
+      <c r="C12" t="s">
+        <v>880</v>
+      </c>
+      <c r="D12" t="s">
+        <v>902</v>
+      </c>
+      <c r="E12" t="s">
+        <v>903</v>
+      </c>
+      <c r="F12" t="s">
+        <v>904</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>905</v>
+      </c>
+      <c r="C13" t="s">
+        <v>550</v>
+      </c>
+      <c r="D13" t="s">
+        <v>906</v>
+      </c>
+      <c r="E13" t="s">
+        <v>898</v>
+      </c>
+      <c r="F13" t="s">
         <v>897</v>
       </c>
-      <c r="E11" t="s">
-        <v>898</v>
-      </c>
-      <c r="F11" t="s">
-        <v>899</v>
-      </c>
-      <c r="G11" t="s">
-        <v>900</v>
-      </c>
-      <c r="H11" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
-        <v>902</v>
-      </c>
-      <c r="C12" t="s">
-        <v>881</v>
-      </c>
-      <c r="D12" t="s">
-        <v>903</v>
-      </c>
-      <c r="E12" t="s">
-        <v>904</v>
-      </c>
-      <c r="F12" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
-        <v>906</v>
-      </c>
-      <c r="C13" t="s">
-        <v>551</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="G13" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>907</v>
       </c>
-      <c r="E13" t="s">
-        <v>899</v>
-      </c>
-      <c r="F13" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>908</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>909</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>910</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>911</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>913</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>914</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>915</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>916</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>918</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>598</v>
+      </c>
+      <c r="E16" t="s">
         <v>919</v>
       </c>
-      <c r="D16" t="s">
-        <v>599</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>758</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>920</v>
       </c>
-      <c r="F16" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>921</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>922</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>923</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>354</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>924</v>
       </c>
-      <c r="F17" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>925</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>926</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>927</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>928</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>930</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>649</v>
+      </c>
+      <c r="E19" t="s">
+        <v>650</v>
+      </c>
+      <c r="F19" t="s">
         <v>931</v>
       </c>
-      <c r="D19" t="s">
-        <v>650</v>
-      </c>
-      <c r="E19" t="s">
-        <v>651</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>611</v>
+      </c>
+      <c r="D20" t="s">
         <v>933</v>
       </c>
-      <c r="C20" t="s">
-        <v>612</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>934</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>935</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>937</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>938</v>
       </c>
-      <c r="D21" t="s">
-        <v>939</v>
-      </c>
       <c r="E21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F21" t="s">
-        <v>759</v>
+        <v>758</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -5356,7 +5544,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A78F9AF-1FAC-47E1-BE80-6FCBEC6AE4EF}">
   <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5367,424 +5555,487 @@
     <col min="6" max="6" width="30.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>939</v>
+      </c>
+      <c r="C2" t="s">
         <v>940</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>941</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>942</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>943</v>
       </c>
-      <c r="F2" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>944</v>
+      </c>
+      <c r="C3" t="s">
         <v>945</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>946</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>947</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>948</v>
       </c>
-      <c r="F3" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>949</v>
+      </c>
+      <c r="C4" t="s">
         <v>950</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>951</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>952</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>953</v>
       </c>
-      <c r="F4" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>954</v>
+      </c>
+      <c r="C5" t="s">
         <v>955</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>956</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>957</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>958</v>
       </c>
-      <c r="F5" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>959</v>
+      </c>
+      <c r="C6" t="s">
         <v>960</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>961</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>962</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>963</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>965</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>473</v>
+      </c>
+      <c r="E7" t="s">
         <v>966</v>
       </c>
-      <c r="D7" t="s">
-        <v>474</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>943</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>967</v>
       </c>
-      <c r="F7" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>968</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>943</v>
+      </c>
+      <c r="E8" t="s">
         <v>969</v>
       </c>
-      <c r="D8" t="s">
-        <v>944</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>970</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>971</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>972</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>973</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>974</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>975</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>976</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>977</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>592</v>
+      </c>
+      <c r="E10" t="s">
         <v>978</v>
       </c>
-      <c r="D10" t="s">
-        <v>593</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>979</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>980</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>981</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>982</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>983</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>984</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>986</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>987</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>988</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>989</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>990</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>473</v>
+      </c>
+      <c r="D13" t="s">
         <v>991</v>
       </c>
-      <c r="C13" t="s">
-        <v>474</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>992</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>943</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>993</v>
       </c>
-      <c r="F13" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>884</v>
+      </c>
+      <c r="D14" t="s">
         <v>994</v>
       </c>
-      <c r="C14" t="s">
-        <v>885</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>995</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>996</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>997</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>998</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>439</v>
+      </c>
+      <c r="E15" t="s">
+        <v>758</v>
+      </c>
+      <c r="F15" t="s">
         <v>999</v>
       </c>
-      <c r="D15" t="s">
-        <v>440</v>
-      </c>
-      <c r="E15" t="s">
-        <v>759</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>1001</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>950</v>
+      </c>
+      <c r="E16" t="s">
         <v>1002</v>
       </c>
-      <c r="D16" t="s">
-        <v>951</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>1003</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>1005</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>1006</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>1007</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1008</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>473</v>
+      </c>
+      <c r="D18" t="s">
+        <v>598</v>
+      </c>
+      <c r="E18" t="s">
         <v>1010</v>
       </c>
-      <c r="C18" t="s">
-        <v>474</v>
-      </c>
-      <c r="D18" t="s">
-        <v>599</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>1011</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>1012</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>1013</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>957</v>
+      </c>
+      <c r="E19" t="s">
         <v>1014</v>
       </c>
-      <c r="D19" t="s">
-        <v>958</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>1015</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>1016</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>1017</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>891</v>
+      </c>
+      <c r="E20" t="s">
+        <v>473</v>
+      </c>
+      <c r="F20" t="s">
+        <v>193</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>1018</v>
       </c>
-      <c r="D20" t="s">
-        <v>892</v>
-      </c>
-      <c r="E20" t="s">
-        <v>474</v>
-      </c>
-      <c r="F20" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>616</v>
+      </c>
+      <c r="D21" t="s">
+        <v>992</v>
+      </c>
+      <c r="E21" t="s">
         <v>1019</v>
       </c>
-      <c r="C21" t="s">
-        <v>617</v>
-      </c>
-      <c r="D21" t="s">
-        <v>993</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>1020</v>
       </c>
-      <c r="F21" t="s">
-        <v>1021</v>
+      <c r="G21" t="s">
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
@@ -5799,7 +6050,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72A711E-D701-464F-968B-8D974534E4C1}">
   <sheetPr codeName="Sheet24"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5810,424 +6061,487 @@
     <col min="6" max="6" width="39.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
         <v>111</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>112</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>113</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>114</v>
       </c>
-      <c r="F2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
         <v>116</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>117</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>118</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>119</v>
       </c>
-      <c r="F3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" t="s">
         <v>121</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>122</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>123</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>124</v>
       </c>
-      <c r="F4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
         <v>126</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>127</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>128</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>129</v>
       </c>
-      <c r="F5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" t="s">
         <v>131</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>132</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>133</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>134</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>136</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>137</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>138</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>139</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>141</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>142</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>143</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>144</v>
       </c>
-      <c r="F8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>145</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>146</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>147</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>148</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>150</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>151</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>152</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>153</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>155</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>156</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>157</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>158</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>160</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>161</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>162</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>163</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>165</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>166</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>167</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>168</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>170</v>
       </c>
-      <c r="C14" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" t="s">
         <v>1036</v>
       </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" t="s">
+        <v>184</v>
+      </c>
+      <c r="G17" t="s">
         <v>1037</v>
       </c>
-      <c r="F14" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" t="s">
-        <v>174</v>
-      </c>
-      <c r="F15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" t="s">
-        <v>179</v>
-      </c>
-      <c r="F16" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" t="s">
-        <v>182</v>
-      </c>
-      <c r="D17" t="s">
-        <v>183</v>
-      </c>
-      <c r="E17" t="s">
-        <v>184</v>
-      </c>
-      <c r="F17" t="s">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>186</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>187</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>188</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>189</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>191</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>192</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>193</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>194</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>196</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>197</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>198</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>199</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>201</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>202</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>203</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>204</v>
       </c>
-      <c r="F21" t="s">
-        <v>205</v>
+      <c r="G21" t="s">
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
@@ -6241,7 +6555,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD7D2240-117B-4D18-BCE0-42010E13D1ED}">
   <sheetPr codeName="Sheet23"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6252,424 +6566,487 @@
     <col min="6" max="6" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" t="s">
         <v>206</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>207</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>208</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>209</v>
       </c>
-      <c r="F2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" t="s">
         <v>211</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>212</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>213</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" t="s">
         <v>216</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>217</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>218</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>219</v>
       </c>
-      <c r="F4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" t="s">
         <v>221</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>222</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>223</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>224</v>
       </c>
-      <c r="F5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" t="s">
         <v>226</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>227</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>228</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>229</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>231</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>232</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>233</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>234</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>236</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>237</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>238</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>239</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E9" t="s">
         <v>242</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>217</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>243</v>
       </c>
-      <c r="F9" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>244</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>245</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>246</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>247</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>249</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>250</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>251</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>252</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>254</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>255</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>256</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>257</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>259</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>260</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>261</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>262</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" t="s">
         <v>264</v>
       </c>
-      <c r="C14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>265</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>266</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>268</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>269</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>270</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>271</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>273</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>274</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
+        <v>227</v>
+      </c>
+      <c r="F16" t="s">
+        <v>251</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>275</v>
       </c>
-      <c r="E16" t="s">
-        <v>228</v>
-      </c>
-      <c r="F16" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>276</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>277</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>278</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>279</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>281</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>282</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>283</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>284</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>286</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>287</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>288</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>289</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
         <v>291</v>
       </c>
-      <c r="C20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>292</v>
       </c>
-      <c r="E20" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>293</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>294</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>295</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>296</v>
       </c>
-      <c r="F21" t="s">
-        <v>297</v>
+      <c r="G21" t="s">
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
@@ -6683,7 +7060,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E89483-92E4-4A13-ADAA-AFC31AED76BC}">
   <sheetPr codeName="Sheet22"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6694,424 +7071,487 @@
     <col min="6" max="6" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" t="s">
         <v>298</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E2" t="s">
         <v>299</v>
       </c>
-      <c r="D2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>300</v>
       </c>
-      <c r="F2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C3" t="s">
         <v>302</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>303</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>304</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>305</v>
       </c>
-      <c r="F3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
         <v>307</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>308</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>309</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>310</v>
       </c>
-      <c r="F4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5" t="s">
         <v>312</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>313</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>314</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>315</v>
       </c>
-      <c r="F5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" t="s">
         <v>317</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>318</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>319</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>320</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>322</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" t="s">
         <v>323</v>
       </c>
-      <c r="D7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>324</v>
       </c>
-      <c r="F7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>325</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>326</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>327</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>313</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>328</v>
       </c>
-      <c r="F8" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>329</v>
       </c>
-      <c r="C9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>330</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>331</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>332</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>333</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>335</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>336</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>337</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>338</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>340</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>341</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>342</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>343</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>345</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E13" t="s">
         <v>346</v>
       </c>
-      <c r="D13" t="s">
-        <v>230</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>347</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>349</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>350</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>351</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>352</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>354</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>355</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>356</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>357</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>359</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>360</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>361</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>362</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>364</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>365</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>366</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>367</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>369</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>313</v>
+      </c>
+      <c r="E18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" t="s">
         <v>370</v>
       </c>
-      <c r="D18" t="s">
-        <v>314</v>
-      </c>
-      <c r="E18" t="s">
-        <v>132</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>372</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>373</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>374</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>375</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>377</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>378</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>379</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>380</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>382</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>341</v>
+      </c>
+      <c r="E21" t="s">
         <v>383</v>
       </c>
-      <c r="D21" t="s">
-        <v>342</v>
-      </c>
-      <c r="E21" t="s">
-        <v>384</v>
-      </c>
       <c r="F21" t="s">
-        <v>284</v>
+        <v>283</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -7125,7 +7565,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DAC7B1-87B1-43FE-8A48-5DA566656E6B}">
   <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7136,424 +7576,487 @@
     <col min="6" max="6" width="31.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C2" t="s">
         <v>385</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>386</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>387</v>
       </c>
-      <c r="E2" t="s">
-        <v>388</v>
-      </c>
       <c r="F2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C3" t="s">
         <v>389</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>390</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>391</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>392</v>
       </c>
-      <c r="F3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" t="s">
         <v>394</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>395</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>396</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>397</v>
       </c>
-      <c r="F4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C5" t="s">
         <v>399</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>400</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>401</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>402</v>
       </c>
-      <c r="F5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C6" t="s">
+        <v>390</v>
+      </c>
+      <c r="D6" t="s">
         <v>404</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>391</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
+        <v>389</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>405</v>
       </c>
-      <c r="E6" t="s">
-        <v>392</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="C7" t="s">
+        <v>406</v>
+      </c>
+      <c r="D7" t="s">
+        <v>407</v>
+      </c>
+      <c r="E7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F7" t="s">
+        <v>409</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>410</v>
+      </c>
+      <c r="C8" t="s">
+        <v>411</v>
+      </c>
+      <c r="D8" t="s">
+        <v>412</v>
+      </c>
+      <c r="E8" t="s">
+        <v>413</v>
+      </c>
+      <c r="F8" t="s">
+        <v>414</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" t="s">
+        <v>416</v>
+      </c>
+      <c r="D9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E9" t="s">
+        <v>417</v>
+      </c>
+      <c r="F9" t="s">
+        <v>418</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C10" t="s">
+        <v>389</v>
+      </c>
+      <c r="D10" t="s">
+        <v>420</v>
+      </c>
+      <c r="E10" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>406</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="F10" t="s">
+        <v>421</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" t="s">
+        <v>423</v>
+      </c>
+      <c r="D11" t="s">
+        <v>424</v>
+      </c>
+      <c r="E11" t="s">
+        <v>425</v>
+      </c>
+      <c r="F11" t="s">
+        <v>426</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C12" t="s">
+        <v>391</v>
+      </c>
+      <c r="D12" t="s">
+        <v>389</v>
+      </c>
+      <c r="E12" t="s">
+        <v>399</v>
+      </c>
+      <c r="F12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C13" t="s">
+        <v>429</v>
+      </c>
+      <c r="D13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E13" t="s">
+        <v>431</v>
+      </c>
+      <c r="F13" t="s">
+        <v>178</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" t="s">
+        <v>433</v>
+      </c>
+      <c r="D14" t="s">
+        <v>434</v>
+      </c>
+      <c r="E14" t="s">
+        <v>435</v>
+      </c>
+      <c r="F14" t="s">
+        <v>436</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C15" t="s">
+        <v>438</v>
+      </c>
+      <c r="D15" t="s">
+        <v>439</v>
+      </c>
+      <c r="E15" t="s">
+        <v>440</v>
+      </c>
+      <c r="F15" t="s">
         <v>407</v>
       </c>
-      <c r="D7" t="s">
-        <v>408</v>
-      </c>
-      <c r="E7" t="s">
-        <v>409</v>
-      </c>
-      <c r="F7" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>411</v>
-      </c>
-      <c r="C8" t="s">
-        <v>412</v>
-      </c>
-      <c r="D8" t="s">
-        <v>413</v>
-      </c>
-      <c r="E8" t="s">
-        <v>414</v>
-      </c>
-      <c r="F8" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>416</v>
-      </c>
-      <c r="C9" t="s">
-        <v>417</v>
-      </c>
-      <c r="D9" t="s">
-        <v>408</v>
-      </c>
-      <c r="E9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F9" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="G15" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>441</v>
+      </c>
+      <c r="C16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D16" t="s">
+        <v>362</v>
+      </c>
+      <c r="E16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F16" t="s">
+        <v>444</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
+        <v>445</v>
+      </c>
+      <c r="C17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" t="s">
+        <v>446</v>
+      </c>
+      <c r="E17" t="s">
         <v>420</v>
       </c>
-      <c r="C10" t="s">
-        <v>390</v>
-      </c>
-      <c r="D10" t="s">
-        <v>421</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F17" t="s">
+        <v>447</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
+        <v>448</v>
+      </c>
+      <c r="C18" t="s">
+        <v>449</v>
+      </c>
+      <c r="D18" t="s">
+        <v>450</v>
+      </c>
+      <c r="E18" t="s">
+        <v>451</v>
+      </c>
+      <c r="F18" t="s">
+        <v>452</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>453</v>
+      </c>
+      <c r="C19" t="s">
+        <v>454</v>
+      </c>
+      <c r="D19" t="s">
         <v>391</v>
       </c>
-      <c r="F10" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>423</v>
-      </c>
-      <c r="C11" t="s">
-        <v>424</v>
-      </c>
-      <c r="D11" t="s">
-        <v>425</v>
-      </c>
-      <c r="E11" t="s">
-        <v>426</v>
-      </c>
-      <c r="F11" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
-        <v>428</v>
-      </c>
-      <c r="C12" t="s">
-        <v>392</v>
-      </c>
-      <c r="D12" t="s">
-        <v>390</v>
-      </c>
-      <c r="E12" t="s">
-        <v>400</v>
-      </c>
-      <c r="F12" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C13" t="s">
-        <v>430</v>
-      </c>
-      <c r="D13" t="s">
-        <v>431</v>
-      </c>
-      <c r="E13" t="s">
-        <v>432</v>
-      </c>
-      <c r="F13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
-        <v>433</v>
-      </c>
-      <c r="C14" t="s">
-        <v>434</v>
-      </c>
-      <c r="D14" t="s">
-        <v>435</v>
-      </c>
-      <c r="E14" t="s">
-        <v>436</v>
-      </c>
-      <c r="F14" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C15" t="s">
-        <v>439</v>
-      </c>
-      <c r="D15" t="s">
-        <v>440</v>
-      </c>
-      <c r="E15" t="s">
-        <v>441</v>
-      </c>
-      <c r="F15" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
-        <v>442</v>
-      </c>
-      <c r="C16" t="s">
-        <v>443</v>
-      </c>
-      <c r="D16" t="s">
-        <v>363</v>
-      </c>
-      <c r="E16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F16" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
-        <v>446</v>
-      </c>
-      <c r="C17" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" t="s">
-        <v>447</v>
-      </c>
-      <c r="E17" t="s">
-        <v>421</v>
-      </c>
-      <c r="F17" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
-        <v>449</v>
-      </c>
-      <c r="C18" t="s">
-        <v>450</v>
-      </c>
-      <c r="D18" t="s">
-        <v>451</v>
-      </c>
-      <c r="E18" t="s">
-        <v>452</v>
-      </c>
-      <c r="F18" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
-        <v>454</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>455</v>
       </c>
-      <c r="D19" t="s">
-        <v>392</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>456</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>458</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>459</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>460</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>461</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>463</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>464</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>465</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>466</v>
       </c>
-      <c r="F21" t="s">
-        <v>467</v>
+      <c r="G21" t="s">
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -7567,7 +8070,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7430C8AE-096C-4C5F-AD96-215138AE7EE2}">
   <sheetPr codeName="Sheet20"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7578,424 +8081,487 @@
     <col min="6" max="6" width="37.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" t="s">
         <v>468</v>
       </c>
-      <c r="C2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>469</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>470</v>
       </c>
-      <c r="F2" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E3" t="s">
         <v>472</v>
       </c>
-      <c r="D3" t="s">
-        <v>390</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>473</v>
       </c>
-      <c r="F3" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C4" t="s">
         <v>475</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>476</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F4" t="s">
         <v>477</v>
       </c>
-      <c r="E4" t="s">
-        <v>379</v>
-      </c>
-      <c r="F4" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C5" t="s">
         <v>479</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>480</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>481</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>482</v>
       </c>
-      <c r="F5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C6" t="s">
         <v>484</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>485</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>486</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>487</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>489</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>490</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>491</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>492</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>494</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>495</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>496</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>497</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>499</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>379</v>
+      </c>
+      <c r="E9" t="s">
         <v>500</v>
       </c>
-      <c r="D9" t="s">
-        <v>380</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>501</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>503</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>504</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>439</v>
+      </c>
+      <c r="F10" t="s">
         <v>505</v>
       </c>
-      <c r="E10" t="s">
-        <v>440</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>507</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>508</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>509</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>510</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" t="s">
         <v>512</v>
       </c>
-      <c r="C12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>499</v>
+      </c>
+      <c r="F12" t="s">
+        <v>500</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>513</v>
       </c>
-      <c r="E12" t="s">
-        <v>500</v>
-      </c>
-      <c r="F12" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>514</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>343</v>
+      </c>
+      <c r="E13" t="s">
+        <v>471</v>
+      </c>
+      <c r="F13" t="s">
+        <v>468</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>515</v>
       </c>
-      <c r="D13" t="s">
-        <v>344</v>
-      </c>
-      <c r="E13" t="s">
-        <v>472</v>
-      </c>
-      <c r="F13" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>516</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>517</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>518</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>519</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>521</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>522</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>523</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>524</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>526</v>
       </c>
-      <c r="C16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>283</v>
+      </c>
+      <c r="D17" t="s">
         <v>527</v>
       </c>
-      <c r="C17" t="s">
-        <v>284</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>528</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>529</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>531</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>532</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>533</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>534</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>536</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>409</v>
+      </c>
+      <c r="E19" t="s">
         <v>537</v>
       </c>
-      <c r="D19" t="s">
-        <v>410</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>407</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>538</v>
       </c>
-      <c r="F19" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>539</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>540</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>541</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>542</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>544</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>545</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>546</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>547</v>
       </c>
-      <c r="F21" t="s">
-        <v>548</v>
+      <c r="G21" t="s">
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -8009,7 +8575,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB018260-721C-4374-A1DF-FAC2F92EA092}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8020,424 +8586,487 @@
     <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C2" t="s">
         <v>549</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>550</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>551</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>552</v>
       </c>
-      <c r="F2" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>553</v>
+      </c>
+      <c r="C3" t="s">
         <v>554</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>555</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>556</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>557</v>
       </c>
-      <c r="F3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C4" t="s">
         <v>559</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>560</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>561</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>562</v>
       </c>
-      <c r="F4" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>563</v>
+      </c>
+      <c r="C5" t="s">
         <v>564</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>565</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>566</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>567</v>
       </c>
-      <c r="F5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>568</v>
+      </c>
+      <c r="C6" t="s">
         <v>569</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>570</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>571</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>572</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" t="s">
         <v>574</v>
       </c>
-      <c r="C7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" t="s">
         <v>575</v>
       </c>
-      <c r="E7" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>577</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>578</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>579</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>580</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>582</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>583</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>584</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>585</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>587</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>588</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>589</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>590</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" t="s">
         <v>592</v>
       </c>
-      <c r="C11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>593</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>594</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>596</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>597</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>598</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>599</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>601</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>602</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>603</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>604</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>606</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>607</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>608</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>609</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>611</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>612</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>613</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>614</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>616</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>617</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>618</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>619</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>621</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>622</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F17" t="s">
         <v>623</v>
       </c>
-      <c r="E17" t="s">
-        <v>193</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>625</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>626</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>627</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>628</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>630</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>631</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>632</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>633</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>472</v>
+      </c>
+      <c r="D20" t="s">
         <v>635</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>473</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>636</v>
       </c>
-      <c r="E20" t="s">
-        <v>474</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>638</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>639</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>640</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>641</v>
       </c>
-      <c r="F21" t="s">
-        <v>642</v>
+      <c r="G21" t="s">
+        <v>1038</v>
       </c>
     </row>
   </sheetData>
@@ -8451,7 +9080,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8351E4E9-CD74-46F8-B21D-9F8F984B8DD5}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8462,424 +9091,487 @@
     <col min="6" max="6" width="45.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F2" t="s">
         <v>719</v>
       </c>
-      <c r="C2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D2" t="s">
-        <v>624</v>
-      </c>
-      <c r="E2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F2" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C3" t="s">
         <v>721</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>722</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>723</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>724</v>
       </c>
-      <c r="F3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>725</v>
+      </c>
+      <c r="C4" t="s">
         <v>726</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>727</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>728</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>729</v>
       </c>
-      <c r="F4" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>730</v>
+      </c>
+      <c r="C5" t="s">
         <v>731</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>732</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>733</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>734</v>
       </c>
-      <c r="F5" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>735</v>
+      </c>
+      <c r="C6" t="s">
+        <v>473</v>
+      </c>
+      <c r="D6" t="s">
         <v>736</v>
       </c>
-      <c r="C6" t="s">
-        <v>474</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>737</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>738</v>
       </c>
-      <c r="F6" t="s">
+      <c r="C7" t="s">
+        <v>739</v>
+      </c>
+      <c r="D7" t="s">
+        <v>622</v>
+      </c>
+      <c r="E7" t="s">
+        <v>740</v>
+      </c>
+      <c r="F7" t="s">
+        <v>741</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>742</v>
+      </c>
+      <c r="C8" t="s">
+        <v>743</v>
+      </c>
+      <c r="D8" t="s">
+        <v>744</v>
+      </c>
+      <c r="E8" t="s">
+        <v>745</v>
+      </c>
+      <c r="F8" t="s">
+        <v>447</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>746</v>
+      </c>
+      <c r="C9" t="s">
+        <v>612</v>
+      </c>
+      <c r="D9" t="s">
+        <v>747</v>
+      </c>
+      <c r="E9" t="s">
+        <v>613</v>
+      </c>
+      <c r="F9" t="s">
+        <v>611</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>748</v>
+      </c>
+      <c r="C10" t="s">
+        <v>749</v>
+      </c>
+      <c r="D10" t="s">
+        <v>750</v>
+      </c>
+      <c r="E10" t="s">
+        <v>751</v>
+      </c>
+      <c r="F10" t="s">
+        <v>733</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>752</v>
+      </c>
+      <c r="C11" t="s">
+        <v>753</v>
+      </c>
+      <c r="D11" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>739</v>
-      </c>
-      <c r="C7" t="s">
-        <v>740</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E11" t="s">
         <v>623</v>
       </c>
-      <c r="E7" t="s">
-        <v>741</v>
-      </c>
-      <c r="F7" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>743</v>
-      </c>
-      <c r="C8" t="s">
-        <v>744</v>
-      </c>
-      <c r="D8" t="s">
-        <v>745</v>
-      </c>
-      <c r="E8" t="s">
-        <v>746</v>
-      </c>
-      <c r="F8" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>747</v>
-      </c>
-      <c r="C9" t="s">
-        <v>613</v>
-      </c>
-      <c r="D9" t="s">
-        <v>748</v>
-      </c>
-      <c r="E9" t="s">
-        <v>614</v>
-      </c>
-      <c r="F9" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
-        <v>749</v>
-      </c>
-      <c r="C10" t="s">
-        <v>750</v>
-      </c>
-      <c r="D10" t="s">
-        <v>751</v>
-      </c>
-      <c r="E10" t="s">
-        <v>752</v>
-      </c>
-      <c r="F10" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>753</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>754</v>
       </c>
-      <c r="D11" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11" t="s">
-        <v>624</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>756</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>757</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>473</v>
+      </c>
+      <c r="F12" t="s">
         <v>758</v>
       </c>
-      <c r="E12" t="s">
-        <v>474</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>760</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>761</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>439</v>
+      </c>
+      <c r="F13" t="s">
+        <v>407</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>762</v>
       </c>
-      <c r="E13" t="s">
-        <v>440</v>
-      </c>
-      <c r="F13" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>763</v>
       </c>
-      <c r="C14" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>764</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>765</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>766</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>767</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>769</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>770</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>771</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>772</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" t="s">
+        <v>473</v>
+      </c>
+      <c r="E17" t="s">
+        <v>575</v>
+      </c>
+      <c r="F17" t="s">
+        <v>192</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>774</v>
       </c>
-      <c r="C17" t="s">
-        <v>198</v>
-      </c>
-      <c r="D17" t="s">
-        <v>474</v>
-      </c>
-      <c r="E17" t="s">
-        <v>576</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="C18" t="s">
+        <v>757</v>
+      </c>
+      <c r="D18" t="s">
+        <v>775</v>
+      </c>
+      <c r="E18" t="s">
+        <v>776</v>
+      </c>
+      <c r="F18" t="s">
+        <v>777</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>778</v>
+      </c>
+      <c r="C19" t="s">
+        <v>779</v>
+      </c>
+      <c r="D19" t="s">
+        <v>780</v>
+      </c>
+      <c r="E19" t="s">
+        <v>781</v>
+      </c>
+      <c r="F19" t="s">
+        <v>782</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>783</v>
+      </c>
+      <c r="C20" t="s">
+        <v>784</v>
+      </c>
+      <c r="D20" t="s">
+        <v>529</v>
+      </c>
+      <c r="E20" t="s">
+        <v>785</v>
+      </c>
+      <c r="F20" t="s">
+        <v>786</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
+        <v>787</v>
+      </c>
+      <c r="C21" t="s">
+        <v>788</v>
+      </c>
+      <c r="D21" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
-        <v>775</v>
-      </c>
-      <c r="C18" t="s">
-        <v>758</v>
-      </c>
-      <c r="D18" t="s">
-        <v>776</v>
-      </c>
-      <c r="E18" t="s">
-        <v>777</v>
-      </c>
-      <c r="F18" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
-        <v>779</v>
-      </c>
-      <c r="C19" t="s">
-        <v>780</v>
-      </c>
-      <c r="D19" t="s">
-        <v>781</v>
-      </c>
-      <c r="E19" t="s">
-        <v>782</v>
-      </c>
-      <c r="F19" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
-        <v>784</v>
-      </c>
-      <c r="C20" t="s">
-        <v>785</v>
-      </c>
-      <c r="D20" t="s">
-        <v>530</v>
-      </c>
-      <c r="E20" t="s">
-        <v>786</v>
-      </c>
-      <c r="F20" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
-        <v>788</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>789</v>
       </c>
-      <c r="D21" t="s">
-        <v>194</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>790</v>
       </c>
-      <c r="F21" t="s">
-        <v>791</v>
+      <c r="G21" t="s">
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -8893,7 +9585,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC61B0B9-B46B-49A4-A5AF-FF522A287AEB}">
   <sheetPr codeName="Sheet17"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8904,424 +9596,487 @@
     <col min="6" max="6" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1024</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1025</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1026</v>
       </c>
-      <c r="E1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C2" t="s">
         <v>643</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E2" t="s">
         <v>644</v>
       </c>
-      <c r="D2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>645</v>
       </c>
-      <c r="F2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>646</v>
+      </c>
+      <c r="C3" t="s">
         <v>647</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>648</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>649</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>650</v>
       </c>
-      <c r="F3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>651</v>
+      </c>
+      <c r="C4" t="s">
         <v>652</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>653</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>654</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>655</v>
       </c>
-      <c r="F4" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>656</v>
+      </c>
+      <c r="C5" t="s">
         <v>657</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>658</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>659</v>
       </c>
-      <c r="E5" t="s">
-        <v>660</v>
-      </c>
       <c r="F5" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>660</v>
+      </c>
+      <c r="C6" t="s">
         <v>661</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>662</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>663</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>664</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>666</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>667</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>668</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>669</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>671</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>672</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>673</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>674</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C9" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>484</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>676</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
+        <v>485</v>
+      </c>
+      <c r="F9" t="s">
         <v>677</v>
       </c>
-      <c r="E9" t="s">
-        <v>486</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" t="s">
         <v>679</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
+        <v>623</v>
+      </c>
+      <c r="F10" t="s">
         <v>193</v>
       </c>
-      <c r="D10" t="s">
+      <c r="G10" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>680</v>
       </c>
-      <c r="E10" t="s">
-        <v>624</v>
-      </c>
-      <c r="F10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>645</v>
+      </c>
+      <c r="D11" t="s">
         <v>681</v>
       </c>
-      <c r="C11" t="s">
-        <v>646</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>682</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>333</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
         <v>683</v>
       </c>
-      <c r="F11" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>456</v>
+      </c>
+      <c r="D12" t="s">
+        <v>550</v>
+      </c>
+      <c r="E12" t="s">
         <v>684</v>
       </c>
-      <c r="C12" t="s">
-        <v>457</v>
-      </c>
-      <c r="D12" t="s">
-        <v>551</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>685</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>687</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
         <v>688</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>71</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>689</v>
       </c>
-      <c r="F13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>333</v>
+      </c>
+      <c r="D14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" t="s">
         <v>690</v>
       </c>
-      <c r="C14" t="s">
-        <v>334</v>
-      </c>
-      <c r="D14" t="s">
-        <v>230</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>691</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>693</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>694</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>695</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>696</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" t="s">
         <v>698</v>
       </c>
-      <c r="C16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
         <v>699</v>
       </c>
-      <c r="F16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>440</v>
+      </c>
+      <c r="D17" t="s">
         <v>700</v>
       </c>
-      <c r="C17" t="s">
-        <v>441</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>701</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>598</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>702</v>
       </c>
-      <c r="F17" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>703</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>283</v>
+      </c>
+      <c r="E18" t="s">
         <v>704</v>
       </c>
-      <c r="D18" t="s">
-        <v>284</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>705</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>707</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>666</v>
+      </c>
+      <c r="E19" t="s">
         <v>708</v>
       </c>
-      <c r="D19" t="s">
-        <v>667</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>709</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>711</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>712</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>713</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>714</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>716</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>423</v>
+      </c>
+      <c r="E21" t="s">
+        <v>666</v>
+      </c>
+      <c r="F21" t="s">
         <v>717</v>
       </c>
-      <c r="D21" t="s">
-        <v>424</v>
-      </c>
-      <c r="E21" t="s">
-        <v>667</v>
-      </c>
-      <c r="F21" t="s">
-        <v>718</v>
+      <c r="G21" t="s">
+        <v>1037</v>
       </c>
     </row>
   </sheetData>

--- a/Data/FM/FM_Quizzes.xlsx
+++ b/Data/FM/FM_Quizzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\FM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DD5962-33A4-46BD-BFDA-F6302B8825B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0C7CAA-8443-4333-805B-0419CC9908B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="757" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="757" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="26" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1041">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -3225,6 +3225,9 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>Financial Activity</t>
   </si>
 </sst>
 </file>
@@ -3524,7 +3527,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{63EC1C8D-A8CD-43FA-A1B1-28B0E604F8EB}" name="Invoked_FunctionQuery1" displayName="Invoked_FunctionQuery1" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{63EC1C8D-A8CD-43FA-A1B1-28B0E604F8EB}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{0B0F324B-E1E8-4274-9B6B-5190B616D6EE}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{0B0F324B-E1E8-4274-9B6B-5190B616D6EE}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{F740AA24-08B7-45E9-B075-4A2744B3E586}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{A49013DD-A5EE-4E4D-B123-059F6F1D7EDB}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{248B5DEC-50F5-4147-ABC7-491DA6D55500}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3540,7 +3543,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{017D5C77-CB0B-402E-834D-A15D50F5641F}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{017D5C77-CB0B-402E-834D-A15D50F5641F}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{455AAFE5-40EA-45C1-BB67-3AA5BB08AAAC}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{455AAFE5-40EA-45C1-BB67-3AA5BB08AAAC}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{69D6F014-6AD2-45E3-9D63-2816FE591192}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{55D809B5-6578-4F90-8311-041B24B1C6D8}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{AEBD9F8B-A433-4E8B-BC2E-4C9F0CB1CBD2}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3556,7 +3559,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{E1E1CE77-F73A-4C77-B7C6-D62035F7A306}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{E1E1CE77-F73A-4C77-B7C6-D62035F7A306}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A3BE2E0E-9AA3-4D1B-A484-F9FD1084EDBF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A3BE2E0E-9AA3-4D1B-A484-F9FD1084EDBF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E12C8D8B-9C25-45FB-9FAD-05645D0D9E44}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{155E75DD-3437-4080-8BFF-3A7960EBACC9}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{D8AA8A38-D9B2-4B54-A517-75118643B1EA}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3572,7 +3575,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{67AB4AF6-7B9D-4850-BDC4-FBB9B831EFBF}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{67AB4AF6-7B9D-4850-BDC4-FBB9B831EFBF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00EC8F79-0F3F-4A99-8F25-0D3FF9746F88}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{00EC8F79-0F3F-4A99-8F25-0D3FF9746F88}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{3E0A8AE2-A129-4867-A441-234C7C525CF2}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{8662F21C-DEC6-4ED2-8FFE-3C98A97EFC59}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{9CDA9D71-2DD8-4C4F-A45F-BFBBD2361D0C}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3588,7 +3591,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{CE4733E6-32BE-45FE-AA55-0A6BED8407E2}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{CE4733E6-32BE-45FE-AA55-0A6BED8407E2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{970B163D-4323-4439-ACCC-57144CBFC96C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{970B163D-4323-4439-ACCC-57144CBFC96C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{3B6AE74A-F231-4EBC-9C83-292BDE188133}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{DB3BBDA9-7631-451D-B577-BDE147CFED88}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7D7A4AAE-0514-45B7-884C-69037B40B09F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3604,7 +3607,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AFBB01ED-FD1B-447E-8286-C2818ABDE744}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{AFBB01ED-FD1B-447E-8286-C2818ABDE744}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E19626C5-FCE8-44CF-A56F-23C57B0BC645}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{E19626C5-FCE8-44CF-A56F-23C57B0BC645}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{D96BCFFE-2E7C-450A-A9F7-94A50DCF15CB}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F5701FBF-B3DF-4158-AEB1-A94BD33E998F}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{1ACA846A-1510-4EDF-8887-8A4E7FE37C12}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3620,7 +3623,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{FEB41DDA-B23B-492D-926A-4D66FE12C87B}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{FEB41DDA-B23B-492D-926A-4D66FE12C87B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F9816592-9F0B-4B65-BCFF-117EA765AC46}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{F9816592-9F0B-4B65-BCFF-117EA765AC46}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{324013E0-A8F5-4485-AF7B-8B702970A320}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{BF1653F1-0A98-47E6-85C3-F558B4E0B464}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{0346CF58-1703-49DE-8ED6-980B795B8087}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3636,7 +3639,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{0BEF02E7-AA42-46C0-82A2-FF4ABD983B81}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{0BEF02E7-AA42-46C0-82A2-FF4ABD983B81}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2BA36A9E-F952-41A9-9285-D4EB5EDFD6FE}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{2BA36A9E-F952-41A9-9285-D4EB5EDFD6FE}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{08C29924-8CE5-45CB-8D89-E21396FBD34F}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{4F59FA37-D0CA-4C6A-9049-8BAB5A127AA6}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{B38EFD44-4925-4804-B22B-72DC6D40ED1E}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3652,7 +3655,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{0BDEB42C-11DB-466E-9C74-432BD0989372}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{0BDEB42C-11DB-466E-9C74-432BD0989372}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5FEA64B8-065A-4B6F-9CBA-BF6043B59267}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{5FEA64B8-065A-4B6F-9CBA-BF6043B59267}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{E0739EFC-8D32-4632-A844-8680B1137F0E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E82EF2A1-E038-495D-B269-44CB6F0E100D}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7A8E0AC3-28C6-46E2-AEFA-5333A076C763}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3668,7 +3671,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{52C2454F-E770-43E2-9BB5-590374E7D771}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{52C2454F-E770-43E2-9BB5-590374E7D771}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{54A5AC94-05DB-472C-B51F-A1F09CAE24E2}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{54A5AC94-05DB-472C-B51F-A1F09CAE24E2}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{757ADCB9-2554-4E5E-A83E-C2DB4D02C1FD}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{1EE8A824-3E1F-47BD-9F16-29D0E60BCCE0}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{4DD5E5A0-1640-48A3-B08B-75FCCD70538F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3684,7 +3687,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{FF4F6A93-5234-4040-B178-F05987A6590E}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{FF4F6A93-5234-4040-B178-F05987A6590E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{101C3727-056A-4416-BD57-3EAE5F6454E6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{101C3727-056A-4416-BD57-3EAE5F6454E6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{0F2F95F3-90A7-40FE-8826-318209EB5E6D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E123AC86-ED60-48F7-A0B5-47FD96E81FD2}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7B966358-95EC-4170-BC56-B8D418D75480}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3700,7 +3703,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{8B983792-F360-4E8B-8EC5-81F4D09C656B}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{8B983792-F360-4E8B-8EC5-81F4D09C656B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{75936BAC-13D6-4E20-AB43-BB62C3BEB91E}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{75936BAC-13D6-4E20-AB43-BB62C3BEB91E}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{6601D933-532D-4A74-AC60-9BF62DEA6372}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{7532B0F2-8FFC-488B-ACA2-53DE1C59C155}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{DDCE17E7-A1DE-4ADA-8073-F1CADB22105F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -4079,6 +4082,9 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" t="s">

--- a/Data/FM/FM_Quizzes.xlsx
+++ b/Data/FM/FM_Quizzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\FM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0C7CAA-8443-4333-805B-0419CC9908B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F44100-A837-417B-AC68-3D9907134093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="757" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="757" firstSheet="1" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="26" r:id="rId1"/>
@@ -4088,7 +4088,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4134,7 +4134,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4180,7 +4180,7 @@
         <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4203,7 +4203,7 @@
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4272,7 +4272,7 @@
         <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4295,7 +4295,7 @@
         <v>54</v>
       </c>
       <c r="G11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4318,7 +4318,7 @@
         <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4341,7 +4341,7 @@
         <v>66</v>
       </c>
       <c r="G13" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4364,7 +4364,7 @@
         <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4387,7 +4387,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4410,7 +4410,7 @@
         <v>83</v>
       </c>
       <c r="G16" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4433,7 +4433,7 @@
         <v>89</v>
       </c>
       <c r="G17" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>95</v>
       </c>
       <c r="G18" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4502,7 +4502,7 @@
         <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>109</v>
       </c>
       <c r="G21" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
   </sheetData>
@@ -4593,7 +4593,7 @@
         <v>795</v>
       </c>
       <c r="G2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4616,7 +4616,7 @@
         <v>800</v>
       </c>
       <c r="G3" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4639,7 +4639,7 @@
         <v>805</v>
       </c>
       <c r="G4" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4662,7 +4662,7 @@
         <v>807</v>
       </c>
       <c r="G5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4685,7 +4685,7 @@
         <v>812</v>
       </c>
       <c r="G6" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4708,7 +4708,7 @@
         <v>333</v>
       </c>
       <c r="G7" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4731,7 +4731,7 @@
         <v>816</v>
       </c>
       <c r="G8" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4777,7 +4777,7 @@
         <v>283</v>
       </c>
       <c r="G10" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4800,7 +4800,7 @@
         <v>598</v>
       </c>
       <c r="G11" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4823,7 +4823,7 @@
         <v>830</v>
       </c>
       <c r="G12" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4869,7 +4869,7 @@
         <v>612</v>
       </c>
       <c r="G14" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4892,7 +4892,7 @@
         <v>838</v>
       </c>
       <c r="G15" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4915,7 +4915,7 @@
         <v>843</v>
       </c>
       <c r="G16" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4938,7 +4938,7 @@
         <v>847</v>
       </c>
       <c r="G17" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4961,7 +4961,7 @@
         <v>852</v>
       </c>
       <c r="G18" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4984,7 +4984,7 @@
         <v>855</v>
       </c>
       <c r="G19" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5007,7 +5007,7 @@
         <v>407</v>
       </c>
       <c r="G20" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5030,7 +5030,7 @@
         <v>863</v>
       </c>
       <c r="G21" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -5306,7 +5306,7 @@
         <v>900</v>
       </c>
       <c r="G11" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5604,7 +5604,7 @@
         <v>943</v>
       </c>
       <c r="G2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6110,7 +6110,7 @@
         <v>114</v>
       </c>
       <c r="G2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6133,7 +6133,7 @@
         <v>119</v>
       </c>
       <c r="G3" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6179,7 +6179,7 @@
         <v>129</v>
       </c>
       <c r="G5" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6202,7 +6202,7 @@
         <v>134</v>
       </c>
       <c r="G6" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6225,7 +6225,7 @@
         <v>139</v>
       </c>
       <c r="G7" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6248,7 +6248,7 @@
         <v>134</v>
       </c>
       <c r="G8" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6271,7 +6271,7 @@
         <v>148</v>
       </c>
       <c r="G9" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6317,7 +6317,7 @@
         <v>158</v>
       </c>
       <c r="G11" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6340,7 +6340,7 @@
         <v>163</v>
       </c>
       <c r="G12" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6386,7 +6386,7 @@
         <v>1034</v>
       </c>
       <c r="G14" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6409,7 +6409,7 @@
         <v>174</v>
       </c>
       <c r="G15" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6432,7 +6432,7 @@
         <v>179</v>
       </c>
       <c r="G16" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6455,7 +6455,7 @@
         <v>184</v>
       </c>
       <c r="G17" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6501,7 +6501,7 @@
         <v>194</v>
       </c>
       <c r="G19" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6547,7 +6547,7 @@
         <v>204</v>
       </c>
       <c r="G21" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -6615,7 +6615,7 @@
         <v>209</v>
       </c>
       <c r="G2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6638,7 +6638,7 @@
         <v>214</v>
       </c>
       <c r="G3" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6661,7 +6661,7 @@
         <v>219</v>
       </c>
       <c r="G4" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6684,7 +6684,7 @@
         <v>224</v>
       </c>
       <c r="G5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6707,7 +6707,7 @@
         <v>229</v>
       </c>
       <c r="G6" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6730,7 +6730,7 @@
         <v>234</v>
       </c>
       <c r="G7" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6776,7 +6776,7 @@
         <v>217</v>
       </c>
       <c r="G9" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6799,7 +6799,7 @@
         <v>247</v>
       </c>
       <c r="G10" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6845,7 +6845,7 @@
         <v>257</v>
       </c>
       <c r="G12" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6891,7 +6891,7 @@
         <v>266</v>
       </c>
       <c r="G14" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6914,7 +6914,7 @@
         <v>271</v>
       </c>
       <c r="G15" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6937,7 +6937,7 @@
         <v>251</v>
       </c>
       <c r="G16" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7006,7 +7006,7 @@
         <v>289</v>
       </c>
       <c r="G19" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7029,7 +7029,7 @@
         <v>121</v>
       </c>
       <c r="G20" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7052,7 +7052,7 @@
         <v>296</v>
       </c>
       <c r="G21" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -7120,7 +7120,7 @@
         <v>300</v>
       </c>
       <c r="G2" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7143,7 +7143,7 @@
         <v>305</v>
       </c>
       <c r="G3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7166,7 +7166,7 @@
         <v>310</v>
       </c>
       <c r="G4" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7189,7 +7189,7 @@
         <v>315</v>
       </c>
       <c r="G5" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7212,7 +7212,7 @@
         <v>320</v>
       </c>
       <c r="G6" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7235,7 +7235,7 @@
         <v>131</v>
       </c>
       <c r="G7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7258,7 +7258,7 @@
         <v>313</v>
       </c>
       <c r="G8" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7281,7 +7281,7 @@
         <v>122</v>
       </c>
       <c r="G9" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7304,7 +7304,7 @@
         <v>333</v>
       </c>
       <c r="G10" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7327,7 +7327,7 @@
         <v>338</v>
       </c>
       <c r="G11" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7350,7 +7350,7 @@
         <v>343</v>
       </c>
       <c r="G12" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7396,7 +7396,7 @@
         <v>352</v>
       </c>
       <c r="G14" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7419,7 +7419,7 @@
         <v>357</v>
       </c>
       <c r="G15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7442,7 +7442,7 @@
         <v>362</v>
       </c>
       <c r="G16" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7465,7 +7465,7 @@
         <v>367</v>
       </c>
       <c r="G17" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7488,7 +7488,7 @@
         <v>370</v>
       </c>
       <c r="G18" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7511,7 +7511,7 @@
         <v>375</v>
       </c>
       <c r="G19" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7534,7 +7534,7 @@
         <v>380</v>
       </c>
       <c r="G20" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7557,7 +7557,7 @@
         <v>283</v>
       </c>
       <c r="G21" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -7648,7 +7648,7 @@
         <v>392</v>
       </c>
       <c r="G3" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7671,7 +7671,7 @@
         <v>397</v>
       </c>
       <c r="G4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7694,7 +7694,7 @@
         <v>402</v>
       </c>
       <c r="G5" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7740,7 +7740,7 @@
         <v>409</v>
       </c>
       <c r="G7" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7763,7 +7763,7 @@
         <v>414</v>
       </c>
       <c r="G8" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7786,7 +7786,7 @@
         <v>418</v>
       </c>
       <c r="G9" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7832,7 +7832,7 @@
         <v>426</v>
       </c>
       <c r="G11" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7855,7 +7855,7 @@
         <v>390</v>
       </c>
       <c r="G12" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7878,7 +7878,7 @@
         <v>178</v>
       </c>
       <c r="G13" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7901,7 +7901,7 @@
         <v>436</v>
       </c>
       <c r="G14" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7924,7 +7924,7 @@
         <v>407</v>
       </c>
       <c r="G15" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7947,7 +7947,7 @@
         <v>444</v>
       </c>
       <c r="G16" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7970,7 +7970,7 @@
         <v>447</v>
       </c>
       <c r="G17" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8016,7 +8016,7 @@
         <v>456</v>
       </c>
       <c r="G19" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8039,7 +8039,7 @@
         <v>461</v>
       </c>
       <c r="G20" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8062,7 +8062,7 @@
         <v>466</v>
       </c>
       <c r="G21" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
   </sheetData>
@@ -8130,7 +8130,7 @@
         <v>470</v>
       </c>
       <c r="G2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8153,7 +8153,7 @@
         <v>473</v>
       </c>
       <c r="G3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8176,7 +8176,7 @@
         <v>477</v>
       </c>
       <c r="G4" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8199,7 +8199,7 @@
         <v>482</v>
       </c>
       <c r="G5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8222,7 +8222,7 @@
         <v>487</v>
       </c>
       <c r="G6" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8245,7 +8245,7 @@
         <v>492</v>
       </c>
       <c r="G7" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8291,7 +8291,7 @@
         <v>501</v>
       </c>
       <c r="G9" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8429,7 +8429,7 @@
         <v>524</v>
       </c>
       <c r="G15" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8452,7 +8452,7 @@
         <v>123</v>
       </c>
       <c r="G16" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8475,7 +8475,7 @@
         <v>529</v>
       </c>
       <c r="G17" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8521,7 +8521,7 @@
         <v>407</v>
       </c>
       <c r="G19" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8567,7 +8567,7 @@
         <v>547</v>
       </c>
       <c r="G21" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -8635,7 +8635,7 @@
         <v>552</v>
       </c>
       <c r="G2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8658,7 +8658,7 @@
         <v>557</v>
       </c>
       <c r="G3" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8681,7 +8681,7 @@
         <v>562</v>
       </c>
       <c r="G4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8704,7 +8704,7 @@
         <v>567</v>
       </c>
       <c r="G5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8727,7 +8727,7 @@
         <v>572</v>
       </c>
       <c r="G6" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8750,7 +8750,7 @@
         <v>575</v>
       </c>
       <c r="G7" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8796,7 +8796,7 @@
         <v>585</v>
       </c>
       <c r="G9" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8819,7 +8819,7 @@
         <v>590</v>
       </c>
       <c r="G10" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8842,7 +8842,7 @@
         <v>594</v>
       </c>
       <c r="G11" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8865,7 +8865,7 @@
         <v>599</v>
       </c>
       <c r="G12" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8888,7 +8888,7 @@
         <v>604</v>
       </c>
       <c r="G13" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8911,7 +8911,7 @@
         <v>609</v>
       </c>
       <c r="G14" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9003,7 +9003,7 @@
         <v>628</v>
       </c>
       <c r="G18" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9072,7 +9072,7 @@
         <v>641</v>
       </c>
       <c r="G21" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
@@ -9140,7 +9140,7 @@
         <v>719</v>
       </c>
       <c r="G2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9163,7 +9163,7 @@
         <v>724</v>
       </c>
       <c r="G3" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9186,7 +9186,7 @@
         <v>729</v>
       </c>
       <c r="G4" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -9209,7 +9209,7 @@
         <v>734</v>
       </c>
       <c r="G5" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9232,7 +9232,7 @@
         <v>192</v>
       </c>
       <c r="G6" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9255,7 +9255,7 @@
         <v>741</v>
       </c>
       <c r="G7" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -9278,7 +9278,7 @@
         <v>447</v>
       </c>
       <c r="G8" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9301,7 +9301,7 @@
         <v>611</v>
       </c>
       <c r="G9" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9324,7 +9324,7 @@
         <v>733</v>
       </c>
       <c r="G10" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9370,7 +9370,7 @@
         <v>758</v>
       </c>
       <c r="G12" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -9393,7 +9393,7 @@
         <v>407</v>
       </c>
       <c r="G13" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -9416,7 +9416,7 @@
         <v>1030</v>
       </c>
       <c r="G14" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9439,7 +9439,7 @@
         <v>767</v>
       </c>
       <c r="G15" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9462,7 +9462,7 @@
         <v>772</v>
       </c>
       <c r="G16" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9508,7 +9508,7 @@
         <v>777</v>
       </c>
       <c r="G18" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9531,7 +9531,7 @@
         <v>782</v>
       </c>
       <c r="G19" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -9554,7 +9554,7 @@
         <v>786</v>
       </c>
       <c r="G20" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -9668,7 +9668,7 @@
         <v>650</v>
       </c>
       <c r="G3" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9691,7 +9691,7 @@
         <v>655</v>
       </c>
       <c r="G4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -9714,7 +9714,7 @@
         <v>439</v>
       </c>
       <c r="G5" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9737,7 +9737,7 @@
         <v>664</v>
       </c>
       <c r="G6" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9760,7 +9760,7 @@
         <v>669</v>
       </c>
       <c r="G7" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -9806,7 +9806,7 @@
         <v>677</v>
       </c>
       <c r="G9" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9829,7 +9829,7 @@
         <v>193</v>
       </c>
       <c r="G10" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9875,7 +9875,7 @@
         <v>685</v>
       </c>
       <c r="G12" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -9898,7 +9898,7 @@
         <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -9990,7 +9990,7 @@
         <v>598</v>
       </c>
       <c r="G17" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -10013,7 +10013,7 @@
         <v>705</v>
       </c>
       <c r="G18" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -10036,7 +10036,7 @@
         <v>709</v>
       </c>
       <c r="G19" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -10082,7 +10082,7 @@
         <v>717</v>
       </c>
       <c r="G21" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
